--- a/scripts/checks/test_hist/word_order_hist.xlsx
+++ b/scripts/checks/test_hist/word_order_hist.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,56 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3647</v>
+      </c>
+      <c r="D6" t="n">
+        <v>743</v>
+      </c>
+      <c r="E6" t="n">
+        <v>435</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.101598173515982</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8.123110151187905</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7.305518169582773</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8.232183908045977</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8742461989731187</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.021511977671923</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>VS</t>
         </is>
